--- a/data/trans_dic/P3A$yo-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A$yo-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,4; 66,27</t>
+          <t>53,65; 66,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,92; 94,38</t>
+          <t>86,21; 94,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,89; 78,87</t>
+          <t>71,05; 78,94</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,95; 77,9</t>
+          <t>66,9; 77,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,16; 93,78</t>
+          <t>88,39; 93,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,62; 84,74</t>
+          <t>78,58; 84,9</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71,92; 81,46</t>
+          <t>72,27; 80,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,18; 91,85</t>
+          <t>86,41; 92,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,73; 85,94</t>
+          <t>80,56; 85,93</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,92; 71,62</t>
+          <t>57,58; 71,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,45; 94,62</t>
+          <t>86,01; 94,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,16; 86,11</t>
+          <t>75,95; 85,69</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>83,2; 92,03</t>
+          <t>83,75; 91,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,41; 97,92</t>
+          <t>92,16; 97,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,08; 95,29</t>
+          <t>89,86; 95,37</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,88; 81,87</t>
+          <t>71,83; 81,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88,67; 93,7</t>
+          <t>88,98; 94,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,22; 86,82</t>
+          <t>81,37; 86,84</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>67,83; 76,61</t>
+          <t>68,32; 76,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,54; 95,68</t>
+          <t>86,55; 95,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,25; 89,18</t>
+          <t>79,0; 89,27</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,69; 44,51</t>
+          <t>14,31; 44,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>90,83; 94,58</t>
+          <t>90,73; 94,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,8; 69,44</t>
+          <t>36,26; 69,47</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47,57; 66,49</t>
+          <t>46,73; 66,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>90,35; 93,16</t>
+          <t>90,37; 93,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>67,01; 80,34</t>
+          <t>68,12; 80,32</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>166300; 206399</t>
+          <t>167074; 206429</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>248852; 273352</t>
+          <t>249691; 273876</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>426128; 474080</t>
+          <t>427060; 474473</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>347079; 403807</t>
+          <t>346819; 401491</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>453998; 482940</t>
+          <t>455200; 483614</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>812425; 875669</t>
+          <t>812061; 877282</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>226839; 256939</t>
+          <t>227949; 255290</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>299787; 319515</t>
+          <t>300583; 320661</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535459; 570056</t>
+          <t>534332; 569993</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>177915; 223868</t>
+          <t>179981; 223721</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>411274; 450102</t>
+          <t>409158; 449595</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>592483; 678792</t>
+          <t>598681; 675463</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>148317; 164061</t>
+          <t>149298; 163448</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>239133; 253393</t>
+          <t>238500; 253181</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>393720; 416463</t>
+          <t>392750; 416839</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>193814; 220748</t>
+          <t>193669; 219858</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>227944; 240866</t>
+          <t>228734; 241805</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>427778; 457300</t>
+          <t>428595; 457375</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>423462; 478257</t>
+          <t>426531; 480536</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>734978; 812568</t>
+          <t>735039; 813207</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1167712; 1314159</t>
+          <t>1164053; 1315381</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>127098; 413387</t>
+          <t>132880; 414247</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>651951; 678805</t>
+          <t>651164; 679863</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>605873; 1143303</t>
+          <t>596991; 1143817</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1645467; 2299797</t>
+          <t>1616269; 2302431</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3352739; 3457073</t>
+          <t>3353826; 3455773</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4804174; 5760368</t>
+          <t>4883769; 5758566</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$yo-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A$yo-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,65; 66,28</t>
+          <t>51,79; 63,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,21; 94,56</t>
+          <t>87,73; 94,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71,05; 78,94</t>
+          <t>70,86; 77,74</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,9; 77,45</t>
+          <t>68,2; 78,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,39; 93,91</t>
+          <t>87,76; 93,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,58; 84,9</t>
+          <t>79,18; 84,97</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,37%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,27; 80,94</t>
+          <t>71,38; 80,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,41; 92,18</t>
+          <t>86,76; 92,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,56; 85,93</t>
+          <t>80,66; 85,93</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,58; 71,58</t>
+          <t>57,48; 71,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,01; 94,51</t>
+          <t>83,72; 91,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,95; 85,69</t>
+          <t>73,1; 80,88</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>83,75; 91,68</t>
+          <t>83,63; 91,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,16; 97,84</t>
+          <t>90,61; 96,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,86; 95,37</t>
+          <t>88,65; 93,76</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,83; 81,54</t>
+          <t>72,52; 81,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88,98; 94,07</t>
+          <t>89,1; 93,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,37; 86,84</t>
+          <t>81,4; 86,71</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>68,32; 76,97</t>
+          <t>68,31; 76,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,55; 95,75</t>
+          <t>84,86; 90,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,0; 89,27</t>
+          <t>77,81; 82,52</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>68,48%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,31; 44,6</t>
+          <t>39,96; 47,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>90,73; 94,72</t>
+          <t>90,37; 94,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>36,26; 69,47</t>
+          <t>66,06; 70,84</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46,73; 66,57</t>
+          <t>63,75; 67,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>90,37; 93,12</t>
+          <t>89,56; 91,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>68,12; 80,32</t>
+          <t>77,31; 79,47</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>186588</t>
+          <t>183501</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>264925</t>
+          <t>290022</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>451513</t>
+          <t>473523</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>167074; 206429</t>
+          <t>165114; 201308</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>249691; 273876</t>
+          <t>277295; 298652</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>427060; 474473</t>
+          <t>449896; 493567</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>375996</t>
+          <t>388911</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>471212</t>
+          <t>497943</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>847208</t>
+          <t>886854</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>346819; 401491</t>
+          <t>361875; 414307</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>455200; 483614</t>
+          <t>479610; 511814</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>812061; 877282</t>
+          <t>852899; 915286</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>242148</t>
+          <t>240290</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>311471</t>
+          <t>318735</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>553619</t>
+          <t>559025</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>227949; 255290</t>
+          <t>225113; 252900</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>300583; 320661</t>
+          <t>308112; 327186</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>534332; 569993</t>
+          <t>540830; 576194</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>202930</t>
+          <t>240911</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>430401</t>
+          <t>372803</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>633330</t>
+          <t>613715</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>179981; 223721</t>
+          <t>214471; 265382</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>409158; 449595</t>
+          <t>353270; 386126</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>598681; 675463</t>
+          <t>581237; 643085</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>157093</t>
+          <t>180895</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>247405</t>
+          <t>216270</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>404498</t>
+          <t>397164</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>149298; 163448</t>
+          <t>171601; 187858</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>238500; 253181</t>
+          <t>207422; 221388</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>392750; 416839</t>
+          <t>384815; 407013</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>207574</t>
+          <t>209402</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>235819</t>
+          <t>242112</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>443393</t>
+          <t>451515</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>193669; 219858</t>
+          <t>196326; 220581</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>228734; 241805</t>
+          <t>235011; 247694</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>428595; 457375</t>
+          <t>435028; 463444</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>452810</t>
+          <t>522928</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>769182</t>
+          <t>677877</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1221992</t>
+          <t>1200804</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>426531; 480536</t>
+          <t>491654; 550133</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>735039; 813207</t>
+          <t>655192; 695503</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1164053; 1315381</t>
+          <t>1160707; 1231060</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>295470</t>
+          <t>345719</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>667162</t>
+          <t>770160</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>962632</t>
+          <t>1115880</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>132880; 414247</t>
+          <t>318914; 377711</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>651164; 679863</t>
+          <t>751254; 785598</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>596991; 1143817</t>
+          <t>1076302; 1154283</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2120608</t>
+          <t>2312557</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3397577</t>
+          <t>3385923</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5518185</t>
+          <t>5698481</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1616269; 2302431</t>
+          <t>2251481; 2374350</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3353826; 3455773</t>
+          <t>3345644; 3421280</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4883769; 5758566</t>
+          <t>5618246; 5775071</t>
         </is>
       </c>
     </row>
